--- a/backend/fms_core/tests/valid_templates/Normalization_planning_v4_8_0_Sample_Plate.xlsx
+++ b/backend/fms_core/tests/valid_templates/Normalization_planning_v4_8_0_Sample_Plate.xlsx
@@ -2204,7 +2204,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V1002"/>
+  <dimension ref="A1:V1003"/>
   <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="24.3"/>
@@ -2618,46 +2618,16 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
       <c r="C12" s="13"/>
-      <c r="D12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>51</v>
-      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>47</v>
-      </c>
+      <c r="J12" s="2"/>
       <c r="L12" s="14"/>
-      <c r="O12" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="P12" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q12" s="0" t="n">
-        <v>2000</v>
-      </c>
-      <c r="S12" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="V12" s="0" t="n">
-        <v>110</v>
-      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
@@ -2668,13 +2638,13 @@
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>34</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -2682,7 +2652,7 @@
         <v>45</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="L13" s="14"/>
       <c r="O13" s="0" t="n">
@@ -2695,13 +2665,10 @@
         <v>2000</v>
       </c>
       <c r="S13" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="U13" s="0" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="V13" s="0" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2713,13 +2680,13 @@
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>34</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -2727,7 +2694,7 @@
         <v>45</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L14" s="14"/>
       <c r="O14" s="0" t="n">
@@ -2743,26 +2710,55 @@
         <v>10</v>
       </c>
       <c r="U14" s="0" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="V14" s="0" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C15" s="13"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="I15" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="L15" s="14"/>
-      <c r="Q15" s="0" t="str">
-        <f aca="false">IF(AND($O15&lt;&gt;"",$P15&lt;&gt;""), $O15*$P15, "")</f>
-        <v/>
+      <c r="O15" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="P15" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q15" s="0" t="n">
+        <v>2000</v>
+      </c>
+      <c r="S15" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="U15" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="V15" s="0" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2877,7 +2873,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="13"/>
@@ -6083,7 +6079,9 @@
       <c r="C223" s="13"/>
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
-      <c r="I223" s="2"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="2"/>
       <c r="J223" s="2"/>
       <c r="L223" s="14"/>
       <c r="Q223" s="0" t="str">
@@ -10773,8 +10771,13 @@
       <c r="C558" s="13"/>
       <c r="D558" s="2"/>
       <c r="E558" s="2"/>
-      <c r="H558" s="2"/>
+      <c r="I558" s="2"/>
       <c r="J558" s="2"/>
+      <c r="L558" s="14"/>
+      <c r="Q558" s="0" t="str">
+        <f aca="false">IF(AND($O558&lt;&gt;"",$P558&lt;&gt;""), $O558*$P558, "")</f>
+        <v/>
+      </c>
     </row>
     <row r="559" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="2"/>
@@ -10782,7 +10785,7 @@
       <c r="C559" s="13"/>
       <c r="D559" s="2"/>
       <c r="E559" s="2"/>
-      <c r="G559" s="2"/>
+      <c r="H559" s="2"/>
       <c r="J559" s="2"/>
     </row>
     <row r="560" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14757,10 +14760,11 @@
     <row r="1001" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1001" s="2"/>
       <c r="B1001" s="2"/>
-      <c r="C1001" s="2"/>
+      <c r="C1001" s="13"/>
       <c r="D1001" s="2"/>
       <c r="E1001" s="2"/>
       <c r="G1001" s="2"/>
+      <c r="J1001" s="2"/>
     </row>
     <row r="1002" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1002" s="2"/>
@@ -14770,9 +14774,17 @@
       <c r="E1002" s="2"/>
       <c r="G1002" s="2"/>
     </row>
+    <row r="1003" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1003" s="2"/>
+      <c r="B1003" s="2"/>
+      <c r="C1003" s="2"/>
+      <c r="D1003" s="2"/>
+      <c r="E1003" s="2"/>
+      <c r="G1003" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation allowBlank="true" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L6:L557" type="list">
+    <dataValidation allowBlank="true" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L6:L558" type="list">
       <formula1>Index!$A$2:$A$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -14780,19 +14792,19 @@
       <formula1>Index!$J$2:$J$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A6:A1000" type="list">
+    <dataValidation allowBlank="true" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A6:A1001" type="list">
       <formula1>Index!$B$2:$B$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B6:B1000" type="list">
+    <dataValidation allowBlank="true" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B6:B1001" type="list">
       <formula1>Index!$C$2:$C$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J6:J1000" type="list">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J6:J1001" type="list">
       <formula1>IF($L6="384-well plate",Index!$H$2:$H$385,IF($L6="96-well plate", Index!$F$2:$F$97, Index!$H$2:$H$385))</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C6:C1000" type="list">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C6:C1001" type="list">
       <formula1>Index!$K$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
